--- a/S158_131/1.0.0/S-158_131_1_0_0_20260320.xlsx
+++ b/S158_131/1.0.0/S-158_131_1_0_0_20260320.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\git\S-131-Product-Specification-Development\S158_131\1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEC47CE1-6FED-4FFF-BCC4-9DE9553925A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC7BCF1-A52C-4206-B8ED-4C10AF99495D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" tabRatio="647" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28110" windowHeight="18240" tabRatio="647" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="S131ValidationChecks metadata" sheetId="11" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="330">
   <si>
     <t>Document Number</t>
   </si>
@@ -829,18 +829,6 @@
     <t>For each DataCoverage feature where the value of  the attribute minimum display scale is different from other DataCoverage meta features.</t>
   </si>
   <si>
-    <t>[7.3]; [4.3.4]</t>
-  </si>
-  <si>
-    <t>[7.3]; [4.3.1]</t>
-  </si>
-  <si>
-    <t>2.4.7</t>
-  </si>
-  <si>
-    <t>[6.1, 6.2, 7.9.3]</t>
-  </si>
-  <si>
     <t>4.5.1, 4.6.1</t>
   </si>
   <si>
@@ -856,9 +844,6 @@
     <t>11.5.2</t>
   </si>
   <si>
-    <t>6.14.3</t>
-  </si>
-  <si>
     <t>14.2.2</t>
   </si>
   <si>
@@ -910,9 +895,6 @@
     <t>Complex attribute sourceIndication must have at least one sub-attribute populated</t>
   </si>
   <si>
-    <t>6.9.6</t>
-  </si>
-  <si>
     <t>various</t>
   </si>
   <si>
@@ -923,9 +905,6 @@
   </si>
   <si>
     <t>Evaluate necessity for repetition and consider deletion of repeated instance</t>
-  </si>
-  <si>
-    <t>[7.3]; [4.3.5]</t>
   </si>
   <si>
     <t>12.5.2</t>
@@ -1174,6 +1153,39 @@
   </si>
   <si>
     <t>Condition updated.</t>
+  </si>
+  <si>
+    <t>4.3.2</t>
+  </si>
+  <si>
+    <t>4.3.1</t>
+  </si>
+  <si>
+    <t>2.7.1</t>
+  </si>
+  <si>
+    <t>6.1, 6.2, 7.9.3</t>
+  </si>
+  <si>
+    <t>12.10</t>
+  </si>
+  <si>
+    <t>2.4.10.3, 11.6.1</t>
+  </si>
+  <si>
+    <t>2.4.8.2, 19.29</t>
+  </si>
+  <si>
+    <t>6.15.3</t>
+  </si>
+  <si>
+    <t>6.10.6</t>
+  </si>
+  <si>
+    <t>7.6, 12.11</t>
+  </si>
+  <si>
+    <t>[12.13]; [various]</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1457,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1566,6 +1578,18 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1578,20 +1602,14 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1900,14 +1918,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="33.6" customHeight="1">
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="56" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="54"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="58"/>
       <c r="H2" s="27"/>
     </row>
     <row r="3" spans="2:8" s="3" customFormat="1" ht="20.45" customHeight="1">
@@ -2033,7 +2051,7 @@
       <c r="G12" s="28"/>
     </row>
     <row r="13" spans="2:8" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="59" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -2047,7 +2065,7 @@
       <c r="G13" s="28"/>
     </row>
     <row r="14" spans="2:8" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B14" s="55"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="17" t="s">
         <v>36</v>
       </c>
@@ -2059,7 +2077,7 @@
       <c r="G14" s="28"/>
     </row>
     <row r="15" spans="2:8" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B15" s="55"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="18" t="s">
         <v>37</v>
       </c>
@@ -2071,7 +2089,7 @@
       <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:8" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B16" s="55"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="37" t="s">
         <v>29</v>
       </c>
@@ -2083,7 +2101,7 @@
       <c r="G16" s="28"/>
     </row>
     <row r="17" spans="2:7" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B17" s="55"/>
+      <c r="B17" s="59"/>
       <c r="C17" s="19"/>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
@@ -2091,7 +2109,7 @@
       <c r="G17" s="28"/>
     </row>
     <row r="18" spans="2:7" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B18" s="55"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="21"/>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
@@ -2136,7 +2154,7 @@
     <col min="5" max="5" width="67.42578125" style="39" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" style="39" customWidth="1"/>
     <col min="7" max="7" width="18.42578125" style="48" customWidth="1"/>
-    <col min="8" max="8" width="13" style="44" customWidth="1"/>
+    <col min="8" max="8" width="13" style="62" customWidth="1"/>
     <col min="9" max="11" width="10.85546875" style="40"/>
     <col min="12" max="12" width="10.85546875" style="39"/>
     <col min="13" max="13" width="21" style="39" customWidth="1"/>
@@ -2163,25 +2181,25 @@
       <c r="F1" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="57" t="s">
+      <c r="H1" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="58" t="s">
+      <c r="I1" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="58" t="s">
+      <c r="J1" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="58" t="s">
+      <c r="K1" s="53" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="56" t="s">
+      <c r="L1" s="52" t="s">
         <v>172</v>
       </c>
-      <c r="M1" s="59" t="s">
+      <c r="M1" s="54" t="s">
         <v>181</v>
       </c>
     </row>
@@ -2208,7 +2226,7 @@
       <c r="G2" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="42">
+      <c r="H2" s="61">
         <v>7.3</v>
       </c>
       <c r="I2" s="39" t="s">
@@ -2239,10 +2257,10 @@
         <v>120</v>
       </c>
       <c r="G3" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="H3" s="42" t="s">
-        <v>294</v>
+        <v>164</v>
+      </c>
+      <c r="H3" s="61" t="s">
+        <v>319</v>
       </c>
       <c r="I3" s="39" t="s">
         <v>31</v>
@@ -2272,10 +2290,10 @@
         <v>121</v>
       </c>
       <c r="G4" s="49" t="s">
-        <v>180</v>
-      </c>
-      <c r="H4" s="42" t="s">
-        <v>263</v>
+        <v>164</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>320</v>
       </c>
       <c r="I4" s="39" t="s">
         <v>31</v>
@@ -2307,8 +2325,8 @@
       <c r="G5" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H5" s="42" t="s">
-        <v>262</v>
+      <c r="H5" s="61" t="s">
+        <v>320</v>
       </c>
       <c r="I5" s="39" t="s">
         <v>31</v>
@@ -2334,13 +2352,13 @@
       <c r="E6" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="60" t="s">
+      <c r="F6" s="55" t="s">
         <v>123</v>
       </c>
       <c r="G6" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="61" t="s">
         <v>173</v>
       </c>
       <c r="I6" s="39" t="s">
@@ -2375,7 +2393,7 @@
       <c r="G7" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="61" t="s">
         <v>174</v>
       </c>
       <c r="I7" s="39" t="s">
@@ -2410,7 +2428,7 @@
       <c r="G8" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="H8" s="61" t="s">
         <v>244</v>
       </c>
       <c r="I8" s="39" t="s">
@@ -2445,7 +2463,7 @@
       <c r="G9" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="61" t="s">
         <v>175</v>
       </c>
       <c r="I9" s="39" t="s">
@@ -2470,7 +2488,7 @@
         <v>80</v>
       </c>
       <c r="E10" s="49" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F10" s="45" t="s">
         <v>127</v>
@@ -2478,8 +2496,8 @@
       <c r="G10" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H10" s="42" t="s">
-        <v>264</v>
+      <c r="H10" s="61" t="s">
+        <v>321</v>
       </c>
       <c r="I10" s="39" t="s">
         <v>31</v>
@@ -2491,7 +2509,7 @@
         <v>170</v>
       </c>
       <c r="M10" s="39" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="39" thickBot="1">
@@ -2509,7 +2527,7 @@
         <v>81</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F11" s="45" t="s">
         <v>128</v>
@@ -2517,7 +2535,7 @@
       <c r="G11" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="H11" s="42"/>
+      <c r="H11" s="61"/>
       <c r="I11" s="39" t="s">
         <v>31</v>
       </c>
@@ -2540,7 +2558,7 @@
         <v>82</v>
       </c>
       <c r="E12" s="49" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="F12" s="45" t="s">
         <v>129</v>
@@ -2548,7 +2566,7 @@
       <c r="G12" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="H12" s="42"/>
+      <c r="H12" s="61"/>
       <c r="I12" s="39" t="s">
         <v>31</v>
       </c>
@@ -2579,7 +2597,7 @@
       <c r="G13" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="61" t="s">
         <v>176</v>
       </c>
       <c r="I13" s="39" t="s">
@@ -2618,7 +2636,7 @@
       <c r="G14" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="H14" s="42"/>
+      <c r="H14" s="61"/>
       <c r="I14" s="39" t="s">
         <v>31</v>
       </c>
@@ -2649,7 +2667,7 @@
       <c r="G15" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="42" t="s">
+      <c r="H15" s="61" t="s">
         <v>177</v>
       </c>
       <c r="I15" s="39" t="s">
@@ -2682,7 +2700,7 @@
       <c r="G16" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="61" t="s">
         <v>177</v>
       </c>
       <c r="I16" s="39" t="s">
@@ -2715,8 +2733,8 @@
       <c r="G17" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="42" t="s">
-        <v>265</v>
+      <c r="H17" s="61" t="s">
+        <v>322</v>
       </c>
       <c r="I17" s="39" t="s">
         <v>31</v>
@@ -2746,7 +2764,7 @@
         <v>231</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="F18" s="45" t="s">
         <v>134</v>
@@ -2754,7 +2772,7 @@
       <c r="G18" s="49" t="s">
         <v>245</v>
       </c>
-      <c r="H18" s="42"/>
+      <c r="H18" s="61"/>
       <c r="I18" s="39" t="s">
         <v>31</v>
       </c>
@@ -2788,7 +2806,7 @@
       <c r="G19" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H19" s="42">
+      <c r="H19" s="61">
         <v>12.9</v>
       </c>
       <c r="I19" s="40" t="s">
@@ -2821,7 +2839,7 @@
       <c r="G20" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="42">
+      <c r="H20" s="61">
         <v>12.12</v>
       </c>
       <c r="I20" s="40" t="s">
@@ -2854,7 +2872,7 @@
       <c r="G21" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="42">
+      <c r="H21" s="61">
         <v>12.12</v>
       </c>
       <c r="I21" s="40" t="s">
@@ -2887,8 +2905,8 @@
       <c r="G22" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H22" s="42" t="s">
-        <v>266</v>
+      <c r="H22" s="61" t="s">
+        <v>262</v>
       </c>
       <c r="I22" s="40" t="s">
         <v>31</v>
@@ -2897,7 +2915,7 @@
         <v>168</v>
       </c>
       <c r="M22" s="39" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="26.25" thickBot="1">
@@ -2923,8 +2941,8 @@
       <c r="G23" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="42">
-        <v>12.1</v>
+      <c r="H23" s="61" t="s">
+        <v>323</v>
       </c>
       <c r="I23" s="40" t="s">
         <v>31</v>
@@ -2956,8 +2974,8 @@
       <c r="G24" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H24" s="44" t="s">
-        <v>298</v>
+      <c r="H24" s="62" t="s">
+        <v>291</v>
       </c>
       <c r="I24" s="40" t="s">
         <v>31</v>
@@ -2989,8 +3007,8 @@
       <c r="G25" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H25" s="42" t="s">
-        <v>267</v>
+      <c r="H25" s="61" t="s">
+        <v>263</v>
       </c>
       <c r="I25" s="40" t="s">
         <v>31</v>
@@ -3022,8 +3040,8 @@
       <c r="G26" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H26" s="44" t="s">
-        <v>297</v>
+      <c r="H26" s="62" t="s">
+        <v>324</v>
       </c>
       <c r="I26" s="40" t="s">
         <v>31</v>
@@ -3055,8 +3073,8 @@
       <c r="G27" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H27" s="44" t="s">
-        <v>297</v>
+      <c r="H27" s="62" t="s">
+        <v>290</v>
       </c>
       <c r="I27" s="40" t="s">
         <v>31</v>
@@ -3088,8 +3106,8 @@
       <c r="G28" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="H28" s="42" t="s">
-        <v>268</v>
+      <c r="H28" s="61" t="s">
+        <v>264</v>
       </c>
       <c r="I28" s="40" t="s">
         <v>31</v>
@@ -3110,10 +3128,10 @@
         <v>165</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="E29" s="49" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="F29" s="46" t="s">
         <v>146</v>
@@ -3121,8 +3139,8 @@
       <c r="G29" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H29" s="44" t="s">
-        <v>298</v>
+      <c r="H29" s="62" t="s">
+        <v>291</v>
       </c>
       <c r="I29" s="40" t="s">
         <v>31</v>
@@ -3154,7 +3172,7 @@
       <c r="G30" s="49" t="s">
         <v>180</v>
       </c>
-      <c r="H30" s="42" t="s">
+      <c r="H30" s="61" t="s">
         <v>232</v>
       </c>
       <c r="I30" s="40" t="s">
@@ -3217,8 +3235,8 @@
       <c r="G32" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H32" s="44" t="s">
-        <v>290</v>
+      <c r="H32" s="62" t="s">
+        <v>325</v>
       </c>
       <c r="I32" s="40" t="s">
         <v>31</v>
@@ -3250,7 +3268,7 @@
       <c r="G33" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H33" s="44">
+      <c r="H33" s="62">
         <v>19.14</v>
       </c>
       <c r="I33" s="40" t="s">
@@ -3283,8 +3301,8 @@
       <c r="G34" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H34" s="42" t="s">
-        <v>269</v>
+      <c r="H34" s="61" t="s">
+        <v>265</v>
       </c>
       <c r="I34" s="40" t="s">
         <v>31</v>
@@ -3316,8 +3334,8 @@
       <c r="G35" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H35" s="42" t="s">
-        <v>270</v>
+      <c r="H35" s="61" t="s">
+        <v>266</v>
       </c>
       <c r="I35" s="40" t="s">
         <v>31</v>
@@ -3349,7 +3367,7 @@
       <c r="G36" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H36" s="44">
+      <c r="H36" s="62">
         <v>10.1</v>
       </c>
       <c r="I36" s="40" t="s">
@@ -3383,7 +3401,7 @@
       <c r="G37" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H37" s="42">
+      <c r="H37" s="61">
         <v>12.13</v>
       </c>
       <c r="I37" s="40" t="s">
@@ -3409,7 +3427,7 @@
         <v>105</v>
       </c>
       <c r="E38" s="49" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F38" s="46" t="s">
         <v>150</v>
@@ -3417,7 +3435,7 @@
       <c r="G38" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H38" s="42">
+      <c r="H38" s="61">
         <v>12.2</v>
       </c>
       <c r="I38" s="40" t="s">
@@ -3443,7 +3461,7 @@
         <v>106</v>
       </c>
       <c r="E39" s="49" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="F39" s="46" t="s">
         <v>151</v>
@@ -3451,8 +3469,8 @@
       <c r="G39" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H39" s="42" t="s">
-        <v>295</v>
+      <c r="H39" s="61" t="s">
+        <v>288</v>
       </c>
       <c r="I39" s="40" t="s">
         <v>31</v>
@@ -3485,8 +3503,8 @@
       <c r="G40" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H40" s="44" t="s">
-        <v>296</v>
+      <c r="H40" s="62" t="s">
+        <v>289</v>
       </c>
       <c r="I40" s="40" t="s">
         <v>31</v>
@@ -3519,7 +3537,7 @@
       <c r="G41" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H41" s="42">
+      <c r="H41" s="61">
         <v>12.13</v>
       </c>
       <c r="I41" s="40" t="s">
@@ -3553,8 +3571,8 @@
       <c r="G42" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H42" s="42" t="s">
-        <v>271</v>
+      <c r="H42" s="61" t="s">
+        <v>326</v>
       </c>
       <c r="I42" s="40" t="s">
         <v>31</v>
@@ -3586,8 +3604,8 @@
       <c r="G43" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H43" s="42" t="s">
-        <v>271</v>
+      <c r="H43" s="61" t="s">
+        <v>326</v>
       </c>
       <c r="I43" s="40" t="s">
         <v>31</v>
@@ -3619,8 +3637,8 @@
       <c r="G44" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H44" s="42" t="s">
-        <v>271</v>
+      <c r="H44" s="61" t="s">
+        <v>326</v>
       </c>
       <c r="I44" s="40" t="s">
         <v>31</v>
@@ -3652,8 +3670,8 @@
       <c r="G45" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H45" s="42" t="s">
-        <v>272</v>
+      <c r="H45" s="61" t="s">
+        <v>267</v>
       </c>
       <c r="I45" s="40" t="s">
         <v>31</v>
@@ -3685,8 +3703,8 @@
       <c r="G46" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H46" s="42" t="s">
-        <v>272</v>
+      <c r="H46" s="61" t="s">
+        <v>267</v>
       </c>
       <c r="I46" s="40" t="s">
         <v>31</v>
@@ -3710,7 +3728,7 @@
         <v>114</v>
       </c>
       <c r="E47" s="49" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F47" s="46" t="s">
         <v>156</v>
@@ -3718,7 +3736,7 @@
       <c r="G47" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H47" s="42" t="s">
+      <c r="H47" s="61" t="s">
         <v>179</v>
       </c>
       <c r="I47" s="40" t="s">
@@ -3752,13 +3770,13 @@
         <v>71</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G48" s="49" t="s">
         <v>164</v>
       </c>
-      <c r="H48" s="42" t="s">
-        <v>289</v>
+      <c r="H48" s="61" t="s">
+        <v>327</v>
       </c>
       <c r="I48" s="40" t="s">
         <v>31</v>
@@ -3791,8 +3809,8 @@
       <c r="G49" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H49" s="44">
-        <v>7.6</v>
+      <c r="H49" s="62" t="s">
+        <v>328</v>
       </c>
       <c r="I49" s="40" t="s">
         <v>26</v>
@@ -3818,15 +3836,15 @@
         <v>240</v>
       </c>
       <c r="E50" s="49" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="F50" s="46" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="G50" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H50" s="42">
+      <c r="H50" s="61">
         <v>7.5</v>
       </c>
       <c r="I50" s="40" t="s">
@@ -3864,7 +3882,7 @@
       <c r="G51" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H51" s="42">
+      <c r="H51" s="61">
         <v>7.3</v>
       </c>
       <c r="I51" s="40" t="s">
@@ -3888,18 +3906,18 @@
         <v>165</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="E52" s="49" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="F52" s="45" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="G52" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H52" s="42">
+      <c r="H52" s="61">
         <v>12.8</v>
       </c>
       <c r="I52" s="39" t="s">
@@ -3933,7 +3951,7 @@
       <c r="G53" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H53" s="42">
+      <c r="H53" s="61">
         <v>13.1</v>
       </c>
       <c r="I53" s="40" t="s">
@@ -3967,7 +3985,7 @@
       <c r="G54" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H54" s="42">
+      <c r="H54" s="61">
         <v>13.1</v>
       </c>
       <c r="I54" s="40" t="s">
@@ -4001,7 +4019,7 @@
       <c r="G55" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H55" s="42">
+      <c r="H55" s="61">
         <v>13.1</v>
       </c>
       <c r="I55" s="40" t="s">
@@ -4027,7 +4045,7 @@
         <v>256</v>
       </c>
       <c r="E56" s="46" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="F56" s="46" t="s">
         <v>144</v>
@@ -4035,7 +4053,7 @@
       <c r="G56" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="H56" s="42">
+      <c r="H56" s="61">
         <v>14.1</v>
       </c>
       <c r="I56" s="40" t="s">
@@ -4069,7 +4087,7 @@
       <c r="G57" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="H57" s="44" t="s">
+      <c r="H57" s="62" t="s">
         <v>178</v>
       </c>
       <c r="I57" s="40" t="s">
@@ -4092,18 +4110,18 @@
         <v>165</v>
       </c>
       <c r="D58" s="39" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E58" s="39" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="F58" s="39" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G58" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="H58" s="44">
+      <c r="H58" s="62">
         <v>7.3</v>
       </c>
       <c r="I58" s="40" t="s">
@@ -4126,25 +4144,25 @@
         <v>165</v>
       </c>
       <c r="D59" s="39" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E59" s="39" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="F59" s="39" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="G59" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="H59" s="44" t="s">
+      <c r="H59" s="62" t="s">
         <v>176</v>
       </c>
       <c r="I59" s="40" t="s">
         <v>26</v>
       </c>
       <c r="L59" s="39" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="26.25" thickBot="1">
@@ -4160,25 +4178,25 @@
         <v>167</v>
       </c>
       <c r="D60" s="39" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E60" s="39" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F60" s="39" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="G60" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="H60" s="44" t="s">
+      <c r="H60" s="62" t="s">
         <v>176</v>
       </c>
       <c r="I60" s="40" t="s">
         <v>26</v>
       </c>
       <c r="L60" s="39" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="26.25" thickBot="1">
@@ -4194,25 +4212,25 @@
         <v>165</v>
       </c>
       <c r="D61" s="39" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E61" s="39" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F61" s="39" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="G61" s="48" t="s">
-        <v>164</v>
-      </c>
-      <c r="H61" s="44" t="s">
-        <v>290</v>
+        <v>180</v>
+      </c>
+      <c r="H61" s="62" t="s">
+        <v>329</v>
       </c>
       <c r="I61" s="40" t="s">
         <v>26</v>
       </c>
       <c r="L61" s="39" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="26.25" thickBot="1">
@@ -4228,25 +4246,25 @@
         <v>167</v>
       </c>
       <c r="D62" s="39" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E62" s="39" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F62" s="39" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="G62" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="H62" s="44" t="s">
-        <v>290</v>
+      <c r="H62" s="62" t="s">
+        <v>284</v>
       </c>
       <c r="I62" s="40" t="s">
         <v>26</v>
       </c>
       <c r="L62" s="39" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="26.25" thickBot="1">
@@ -4262,25 +4280,25 @@
         <v>167</v>
       </c>
       <c r="D63" s="39" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="E63" s="39" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="F63" s="39" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="G63" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="H63" s="44" t="s">
-        <v>318</v>
+      <c r="H63" s="62" t="s">
+        <v>311</v>
       </c>
       <c r="I63" s="40" t="s">
         <v>26</v>
       </c>
       <c r="L63" s="39" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="26.25" thickBot="1">
@@ -4296,25 +4314,25 @@
         <v>165</v>
       </c>
       <c r="D64" s="39" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E64" s="39" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F64" s="39" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="G64" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="H64" s="44" t="s">
-        <v>317</v>
+      <c r="H64" s="62" t="s">
+        <v>310</v>
       </c>
       <c r="I64" s="40" t="s">
         <v>26</v>
       </c>
       <c r="L64" s="39" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="26.25" thickBot="1">
@@ -4330,25 +4348,25 @@
         <v>167</v>
       </c>
       <c r="D65" s="39" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="E65" s="39" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="F65" s="39" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G65" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="H65" s="44" t="s">
-        <v>317</v>
+      <c r="H65" s="62" t="s">
+        <v>310</v>
       </c>
       <c r="I65" s="40" t="s">
         <v>26</v>
       </c>
       <c r="L65" s="39" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="12.75"/>
